--- a/AAII_Financials/Yearly/ESLOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ESLOY_YR_FIN.xlsx
@@ -2138,10 +2138,10 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>3385000</v>
+        <v>3788900</v>
       </c>
       <c r="E57" s="3">
-        <v>2750800</v>
+        <v>3152500</v>
       </c>
       <c r="F57" s="3">
         <v>2631800</v>
@@ -2204,10 +2204,10 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>2673500</v>
+        <v>2269600</v>
       </c>
       <c r="E59" s="3">
-        <v>2654500</v>
+        <v>2252800</v>
       </c>
       <c r="F59" s="3">
         <v>2986600</v>
